--- a/docs/quality/Technical Debt Register/Technical Debt Register v0.2.xlsx
+++ b/docs/quality/Technical Debt Register/Technical Debt Register v0.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\Desktop\SEN381\Ticketing-System\docs\quality\Technical Debt Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877D648E-681B-4A0D-94DA-C764D14CDB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C1ED88-A1CB-4386-8806-2DE9E454A1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13286" yWindow="0" windowWidth="13543" windowHeight="17914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Technical Debt Register" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Technical Debt Register'!$B$4:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Technical Debt Register'!$B$4:$M$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
   <si>
     <t>Technical Debt Register</t>
   </si>
@@ -164,7 +164,45 @@
     <t>DEC-012 · DEC-015 · OI-01 · OI-16</t>
   </si>
   <si>
-    <t>Known shortcuts and unimplemented baselined rules, why each was accepted, what it costs while unpaid, and what repaying it involves. A debt item is never deleted: a repaid item is marked Repaid with its PR. | Version 0.2 (12/10/2026). Adds TD-003 (the client builds its transition choices from the shared STATUS values rather than being told by the server which transitions the actor may make), raised by E. Lindsay; TD-001 and TD-002 unchanged. Version 0.1 (11/10/2026). Register created during M3 Phase 0 with TD-001 (DEC-011 subscribers not registered) and TD-002 (the FR-1.6 role and group union specified in DB-01 §3.7 but not implemented), both raised by E. Lindsay.</t>
+    <t>TD-004</t>
+  </si>
+  <si>
+    <t>DEC-003 v0.2 deliberately gives civicconnect-app per-collection CRUD with no database-wide role (least privilege, CON-006; DB-01 layer 3), so a destructive grant cannot creep back in. Index creation was left to the schema declarations, and nothing records which credential creates them under a role that cannot. DEC-003’s deploy procedure runs migrations but names no index step. The M3 API test specification (S5) assumed the test cluster’s indexes had been created by hand.</t>
+  </si>
+  <si>
+    <t>FR-1.1, FR-2.6, FR-4.3, FR-6.7, NFR-3.4, NFR-1.4, DEC-003, DEC-015 §3, DEC-016, DEC-017, DB-01, CON-006, PROC-001</t>
+  </si>
+  <si>
+    <t>On the test cluster, observed: the unique and query indexes on requestHistory, requests and users are absent. Elsewhere: any cluster where nobody has created them, which nobody has checked.
+Uniqueness is not enforced by the database. Duplicate history entries under concurrency (DEF-014, DEF-015) and duplicate user emails (DEF-017) are stopped only by application checks where they exist. requests.reference (FR-2.6, “unique, immutable”) has no database guarantee either. No code creates requests yet, so nothing is affected today, but request submission must not ship before this is repaid, or it becomes a defect.
+TTL deletion does not run where the TTL index is missing. On the test cluster the sessions TTL exists; notifications and auditLog were not checked. Notifications not removed at 30 days breaks how DEC-017 purpose A is normally met for them (PROC-001: “normally already removed by the 30-day TTL”), and auditLog entries are not removed at 92 days. The 30-minute session idle limit is enforced in code (DEC-018) either way.
+The text index on requests is absent. No code issues a $text query today. A $text query without a text index fails with an error rather than running slowly, so this must be repaid before FR-4.3 search ships.
+Queries run without the indexes DB-01 justified for them.</t>
+  </si>
+  <si>
+    <t>The application-level guards (idempotency lookup, version check, transition rule) stop duplicate history entries on the code as it stands. Shown by the negative verifications in docs/evidence/M3_API_Negative_Verification.txt. Nothing contains the rest; in particular nothing refuses a duplicate email (DEF-017). The application’s credential is refused listIndexes, so it cannot check its own indexes. The test cluster’s state was listed by hand in the Atlas UI (docs/evidence/M3-indexes/atlas_ui_index_listing_test_cluster.txt).</t>
+  </si>
+  <si>
+    <t>An index-provisioning step run by a privileged, temporary Atlas database user, the pattern PROC-001 uses for retention-operator:
+a dated temporary user with a custom role limited to createIndex and listIndexes on the application’s collections, a short expiry, and deleted after the run;
+the step creates the indexes from the same schema definitions (e.g. Model.createIndexes(), not syncIndexes, which also drops indexes), so there is one source;
+it then runs listIndexes on every collection and compares the result with the schema definitions, with the comparison recorded as evidence.
+Run it on the test cluster first, and re-run the DEF-014 and DEF-015 negative verifications to show the indexes now act. Then run it on staging before the deployment. Record it in a new DEC-003 version (deploy procedure).</t>
+  </si>
+  <si>
+    <t>Before the staging deployment.</t>
+  </si>
+  <si>
+    <t>Ethan</t>
+  </si>
+  <si>
+    <t>DEF-014 · DEF-015 · DEC-003 · DB-01 · PROC-001 · CON-006 · DEF-017 · docs/evidence/M3-indexes/listIndexes_refused_civicconnect-app.txt · docs/evidence/M3-indexes/atlas_ui_index_listing_test_cluster.txt</t>
+  </si>
+  <si>
+    <t>Known shortcuts and unimplemented baselined rules, why each was accepted, what it costs while unpaid, and what repaying it involves. A debt item is never deleted: a repaid item is marked Repaid with its PR. | Version 0.2 (12/10/2026). Adds TD-003 (the client builds its transition choices from the shared STATUS values rather than being told by the server which transitions the actor may make) and TD-004 (no step builds the database indexes the schemas declare, and the application’s database role cannot), both raised by E. Lindsay; TD-001 and TD-002 unchanged. Version 0.1 (11/10/2026). Register created during M3 Phase 0 with TD-001 (DEC-011 subscribers not registered) and TD-002 (the FR-1.6 role and group union specified in DB-01 §3.7 but not implemented), both raised by E. Lindsay.</t>
+  </si>
+  <si>
+    <t>No step builds the database indexes. The Mongoose schemas declare 21 indexes across 10 collections (src/models/*.js, DB-01). They include the unique indexes on users.email (FR-1.1), requests.reference (FR-2.6) and the two on requestHistory (DEC-015 §3, DEC-016 decision 4), and the TTL indexes on sessions (NFR-3.4), notifications and auditLog (DEC-017). Observed on the test cluster (2026-10-12): requestHistory, requests and users, which hold 95, 126 and 112 documents, have only the default _id_ index, so 10 of their 11 declared indexes are absent. sessions has its TTL index, which the application’s credential could not have created (docs/evidence/M3-indexes/atlas_ui_index_listing_test_cluster.txt). Also observed: that credential’s server-reported grants on requestHistory and sessions include no createIndex, it has no database-wide grant (docs/evidence/DB-01_layer3_verification.txt), and it is refused listIndexes on every collection (docs/evidence/M3-indexes/listIndexes_refused_civicconnect-app.txt). Inferred, not observed: that the missing grant is why the indexes are absent; nobody watched an index build fail. No procedure, migration or deploy step builds them with another user. Staging and production are unverified.</t>
   </si>
 </sst>
 </file>
@@ -618,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:M7"/>
+  <dimension ref="B1:M8"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -641,7 +679,7 @@
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B2" s="6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -804,8 +842,47 @@
         <v>41</v>
       </c>
     </row>
+    <row r="8" spans="2:13" ht="360.45" x14ac:dyDescent="0.4">
+      <c r="B8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="4">
+        <f>DATE(2026,10,12)</f>
+        <v>46307</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B4:M7" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="B4:M8" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
